--- a/hospital.xlsx
+++ b/hospital.xlsx
@@ -513,10 +513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Cloudnine Hospital</v>
+        <v>Brindhavvan Areion Hospital</v>
       </c>
       <c r="B9">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C9" t="str">
         <v>Open 24x7</v>
@@ -527,10 +527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Manipal Hospital, Millers Road ( Vikram Hospitals )</v>
+        <v>Ramakrishna Super Speciality Hospital</v>
       </c>
       <c r="B10">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C10" t="str">
         <v>Open 24x7</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Cloudnine Hospital - Whitefield</v>
+        <v>Nethradhama Super Speciality Eye Hospital</v>
       </c>
       <c r="B11">
         <v>4.5</v>

--- a/hospital.xlsx
+++ b/hospital.xlsx
@@ -513,10 +513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Brindhavvan Areion Hospital</v>
+        <v>Cloudnine Hospital</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C9" t="str">
         <v>Open 24x7</v>
@@ -527,10 +527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ramakrishna Super Speciality Hospital</v>
+        <v>Manipal Hospital, Millers Road ( Vikram Hospitals )</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C10" t="str">
         <v>Open 24x7</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nethradhama Super Speciality Eye Hospital</v>
+        <v>Cloudnine Hospital - Whitefield</v>
       </c>
       <c r="B11">
         <v>4.5</v>
